--- a/P&C reports.xlsx
+++ b/P&C reports.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1734" uniqueCount="648">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1735" uniqueCount="648">
   <si>
     <t>CIAO</t>
   </si>
@@ -40,121 +40,121 @@
     <t>NUMERO SECONDA</t>
   </si>
   <si>
+    <t>PRIMA</t>
+  </si>
+  <si>
+    <t>SECONDA</t>
+  </si>
+  <si>
+    <t>Giulia</t>
+  </si>
+  <si>
+    <t>Parisi</t>
+  </si>
+  <si>
+    <t>parisigiulia9@gmail.com</t>
+  </si>
+  <si>
+    <t>Prima serata - 10 Dicembre 2025</t>
+  </si>
+  <si>
+    <t>Gabriele</t>
+  </si>
+  <si>
+    <t>Lentini</t>
+  </si>
+  <si>
+    <t>gabriele.lentini1201@gmail.com</t>
+  </si>
+  <si>
+    <t>Entrambe le serate</t>
+  </si>
+  <si>
+    <t>Patrizia</t>
+  </si>
+  <si>
+    <t>Di girolamo</t>
+  </si>
+  <si>
+    <t>Gaiachiarenza2000@gmail.com</t>
+  </si>
+  <si>
+    <t>Fabiola</t>
+  </si>
+  <si>
+    <t>Fina</t>
+  </si>
+  <si>
+    <t>faby.fina@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stefania </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salerno </t>
+  </si>
+  <si>
+    <t>salerno.stefania979@gmail.com</t>
+  </si>
+  <si>
+    <t>Seconda serata - 11 Dicembre 2025</t>
+  </si>
+  <si>
+    <t>Leonardo</t>
+  </si>
+  <si>
+    <t>Salerno</t>
+  </si>
+  <si>
+    <t>Leonardo.salerno75@gmail.com</t>
+  </si>
+  <si>
+    <t>Luigi</t>
+  </si>
+  <si>
+    <t>Perollo</t>
+  </si>
+  <si>
+    <t>luigiperollo@yahoo.it</t>
+  </si>
+  <si>
+    <t>Gianluca</t>
+  </si>
+  <si>
+    <t>Rubino</t>
+  </si>
+  <si>
+    <t>gianluca_rubino@yahoo.it</t>
+  </si>
+  <si>
+    <t>Maria Teresa</t>
+  </si>
+  <si>
+    <t>riccardorigo4@gmail.com</t>
+  </si>
+  <si>
+    <t>Andrea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Longo </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Andrealongo1997@libero.it </t>
+  </si>
+  <si>
+    <t>Muscarella</t>
+  </si>
+  <si>
+    <t>Andreamu2009@live.it</t>
+  </si>
+  <si>
+    <t>prova</t>
+  </si>
+  <si>
+    <t>wdamiata@gmail.com</t>
+  </si>
+  <si>
     <t>PARTECIPANTI</t>
-  </si>
-  <si>
-    <t>Giulia</t>
-  </si>
-  <si>
-    <t>Parisi</t>
-  </si>
-  <si>
-    <t>parisigiulia9@gmail.com</t>
-  </si>
-  <si>
-    <t>Prima serata - 10 Dicembre 2025</t>
-  </si>
-  <si>
-    <t>Gabriele</t>
-  </si>
-  <si>
-    <t>Lentini</t>
-  </si>
-  <si>
-    <t>gabriele.lentini1201@gmail.com</t>
-  </si>
-  <si>
-    <t>Entrambe le serate</t>
-  </si>
-  <si>
-    <t>Patrizia</t>
-  </si>
-  <si>
-    <t>Di girolamo</t>
-  </si>
-  <si>
-    <t>Gaiachiarenza2000@gmail.com</t>
-  </si>
-  <si>
-    <t>Fabiola</t>
-  </si>
-  <si>
-    <t>Fina</t>
-  </si>
-  <si>
-    <t>faby.fina@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stefania </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Salerno </t>
-  </si>
-  <si>
-    <t>salerno.stefania979@gmail.com</t>
-  </si>
-  <si>
-    <t>Seconda serata - 11 Dicembre 2025</t>
-  </si>
-  <si>
-    <t>Leonardo</t>
-  </si>
-  <si>
-    <t>Salerno</t>
-  </si>
-  <si>
-    <t>Leonardo.salerno75@gmail.com</t>
-  </si>
-  <si>
-    <t>Luigi</t>
-  </si>
-  <si>
-    <t>Perollo</t>
-  </si>
-  <si>
-    <t>luigiperollo@yahoo.it</t>
-  </si>
-  <si>
-    <t>Gianluca</t>
-  </si>
-  <si>
-    <t>Rubino</t>
-  </si>
-  <si>
-    <t>gianluca_rubino@yahoo.it</t>
-  </si>
-  <si>
-    <t>Maria Teresa</t>
-  </si>
-  <si>
-    <t>riccardorigo4@gmail.com</t>
-  </si>
-  <si>
-    <t>Andrea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Longo </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Andrealongo1997@libero.it </t>
-  </si>
-  <si>
-    <t>Muscarella</t>
-  </si>
-  <si>
-    <t>Andreamu2009@live.it</t>
-  </si>
-  <si>
-    <t>prova</t>
-  </si>
-  <si>
-    <t>wdamiata@gmail.com</t>
-  </si>
-  <si>
-    <t>PRIMA</t>
-  </si>
-  <si>
-    <t>SECONDA</t>
   </si>
   <si>
     <t>gabriele</t>
@@ -2596,6 +2596,8 @@
     <col customWidth="1" min="6" max="6" width="30.5"/>
     <col customWidth="1" min="8" max="8" width="17.5"/>
     <col customWidth="1" min="9" max="9" width="24.63"/>
+    <col customWidth="1" min="11" max="11" width="21.75"/>
+    <col customWidth="1" min="12" max="12" width="16.5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2617,23 +2619,27 @@
       <c r="F1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="G1" s="7" t="s">
         <v>7</v>
       </c>
+      <c r="H1" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="7"/>
       <c r="L1" s="7"/>
     </row>
     <row r="2">
       <c r="A2" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E2" s="8">
         <v>1.0</v>
@@ -2641,27 +2647,29 @@
       <c r="F2" s="8">
         <v>0.0</v>
       </c>
-      <c r="K2" s="9">
-        <f t="shared" ref="K2:L2" si="1">SUM(E2:E998)</f>
+      <c r="G2" s="9">
+        <f t="shared" ref="G2:H2" si="1">SUM(E2:E998)</f>
         <v>6</v>
       </c>
-      <c r="L2" s="9">
+      <c r="H2" s="9">
         <f t="shared" si="1"/>
         <v>19</v>
       </c>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
     </row>
     <row r="3">
       <c r="A3" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E3" s="8">
         <v>1.0</v>
@@ -2672,16 +2680,16 @@
     </row>
     <row r="4">
       <c r="A4" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>16</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>15</v>
       </c>
       <c r="E4" s="8">
         <v>2.0</v>
@@ -2692,16 +2700,16 @@
     </row>
     <row r="5">
       <c r="A5" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E5" s="8">
         <v>1.0</v>
@@ -2712,16 +2720,16 @@
     </row>
     <row r="6">
       <c r="A6" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E6" s="8">
         <v>0.0</v>
@@ -2732,16 +2740,16 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" s="5" t="s">
         <v>26</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>25</v>
       </c>
       <c r="E7" s="8">
         <v>0.0</v>
@@ -2752,16 +2760,16 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E8" s="8">
         <v>0.0</v>
@@ -2772,16 +2780,16 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E9" s="8">
         <v>0.0</v>
@@ -2792,16 +2800,16 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E10" s="8">
         <v>0.0</v>
@@ -2812,16 +2820,16 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E11" s="8">
         <v>0.0</v>
@@ -2832,16 +2840,16 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E12" s="8">
         <v>0.0</v>
@@ -2852,16 +2860,16 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E13" s="8">
         <v>1.0</v>
@@ -2908,16 +2916,16 @@
         <v>6</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="I1" s="7"/>
     </row>
     <row r="2">
       <c r="H2" s="7" t="s">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>45</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
@@ -2971,7 +2979,7 @@
       </c>
       <c r="G1" s="10"/>
       <c r="H1" s="7" t="s">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="I1" s="7"/>
     </row>
@@ -2996,10 +3004,10 @@
       </c>
       <c r="G2" s="10"/>
       <c r="H2" s="7" t="s">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>45</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
@@ -3062,7 +3070,7 @@
         <v>59</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D5" s="11" t="s">
         <v>49</v>
@@ -3157,7 +3165,7 @@
         <v>69</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E9" s="12">
         <v>1.0</v>
@@ -3226,7 +3234,7 @@
         <v>79</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E12" s="12">
         <v>2.0</v>
@@ -3318,7 +3326,7 @@
         <v>91</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E16" s="12">
         <v>1.0</v>
@@ -3364,7 +3372,7 @@
         <v>97</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E18" s="12">
         <v>2.0</v>
@@ -3384,10 +3392,10 @@
         <v>99</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E19" s="16">
         <v>1.0</v>
@@ -3410,7 +3418,7 @@
         <v>102</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E20" s="12">
         <v>1.0</v>
@@ -3447,7 +3455,7 @@
     </row>
     <row r="22">
       <c r="A22" s="11" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B22" s="11" t="s">
         <v>106</v>
@@ -3571,7 +3579,7 @@
         <v>122</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E27" s="12">
         <v>1.0</v>
@@ -3654,16 +3662,16 @@
     </row>
     <row r="31">
       <c r="A31" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E31" s="12">
         <v>1.0</v>
@@ -3729,7 +3737,7 @@
         <v>139</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D34" s="11" t="s">
         <v>53</v>
@@ -3755,7 +3763,7 @@
         <v>97</v>
       </c>
       <c r="D35" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E35" s="12">
         <v>1.0</v>
@@ -3861,13 +3869,13 @@
     </row>
     <row r="40">
       <c r="A40" s="11" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B40" s="11" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D40" s="11" t="s">
         <v>49</v>
@@ -3884,13 +3892,13 @@
     </row>
     <row r="41">
       <c r="A41" s="11" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B41" s="11" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D41" s="11" t="s">
         <v>53</v>
@@ -3907,13 +3915,13 @@
     </row>
     <row r="42">
       <c r="A42" s="11" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B42" s="11" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D42" s="11" t="s">
         <v>49</v>
@@ -3959,7 +3967,7 @@
         <v>155</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D44" s="11" t="s">
         <v>49</v>
@@ -3982,7 +3990,7 @@
         <v>157</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D45" s="11" t="s">
         <v>49</v>
@@ -4031,7 +4039,7 @@
         <v>97</v>
       </c>
       <c r="D47" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E47" s="12">
         <v>1.0</v>
@@ -4097,7 +4105,7 @@
         <v>168</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D50" s="11" t="s">
         <v>49</v>
@@ -4114,13 +4122,13 @@
     </row>
     <row r="51">
       <c r="A51" s="11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B51" s="11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D51" s="11" t="s">
         <v>49</v>
@@ -4137,13 +4145,13 @@
     </row>
     <row r="52">
       <c r="A52" s="11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B52" s="11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D52" s="11" t="s">
         <v>49</v>
@@ -4160,13 +4168,13 @@
     </row>
     <row r="53">
       <c r="A53" s="11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B53" s="11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D53" s="11" t="s">
         <v>49</v>
@@ -4189,7 +4197,7 @@
         <v>170</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D54" s="11" t="s">
         <v>49</v>
@@ -4206,13 +4214,13 @@
     </row>
     <row r="55">
       <c r="A55" s="11" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B55" s="11" t="s">
         <v>171</v>
       </c>
       <c r="C55" s="11" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D55" s="11" t="s">
         <v>49</v>
@@ -4235,7 +4243,7 @@
         <v>171</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D56" s="11" t="s">
         <v>49</v>
@@ -4321,13 +4329,13 @@
     </row>
     <row r="60">
       <c r="A60" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B60" s="11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C60" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D60" s="11" t="s">
         <v>53</v>
@@ -4393,10 +4401,10 @@
         <v>187</v>
       </c>
       <c r="B63" s="11" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C63" s="11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D63" s="11" t="s">
         <v>49</v>
@@ -4505,7 +4513,7 @@
     </row>
     <row r="68">
       <c r="A68" s="11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B68" s="11" t="s">
         <v>199</v>
@@ -4721,7 +4729,7 @@
         <v>222</v>
       </c>
       <c r="D77" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E77" s="16">
         <v>1.0</v>
@@ -4810,7 +4818,7 @@
         <v>232</v>
       </c>
       <c r="C81" s="11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D81" s="11" t="s">
         <v>53</v>
@@ -4856,7 +4864,7 @@
         <v>237</v>
       </c>
       <c r="C83" s="11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D83" s="11" t="s">
         <v>53</v>
@@ -5109,7 +5117,7 @@
         <v>260</v>
       </c>
       <c r="C94" s="11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D94" s="11" t="s">
         <v>49</v>
@@ -5126,7 +5134,7 @@
     </row>
     <row r="95">
       <c r="A95" s="11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B95" s="11" t="s">
         <v>261</v>
@@ -5218,7 +5226,7 @@
     </row>
     <row r="99">
       <c r="A99" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B99" s="11" t="s">
         <v>269</v>
@@ -5293,7 +5301,7 @@
         <v>278</v>
       </c>
       <c r="C102" s="11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D102" s="11" t="s">
         <v>49</v>
@@ -5402,7 +5410,7 @@
     </row>
     <row r="107">
       <c r="A107" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B107" s="11" t="s">
         <v>287</v>
@@ -5448,7 +5456,7 @@
     </row>
     <row r="109">
       <c r="A109" s="11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B109" s="11" t="s">
         <v>185</v>
@@ -5477,7 +5485,7 @@
         <v>293</v>
       </c>
       <c r="C110" s="11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D110" s="11" t="s">
         <v>53</v>
@@ -15558,7 +15566,7 @@
         <v>45599.85156443287</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C7" s="23" t="s">
         <v>346</v>
@@ -15581,7 +15589,7 @@
         <v>45611.36980922453</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C8" s="23" t="s">
         <v>348</v>
@@ -15604,7 +15612,7 @@
         <v>45611.544511747685</v>
       </c>
       <c r="B9" s="23" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C9" s="23" t="s">
         <v>350</v>
@@ -15768,7 +15776,7 @@
         <v>362</v>
       </c>
       <c r="C16" s="23" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D16" s="23" t="s">
         <v>363</v>
@@ -15884,7 +15892,7 @@
         <v>372</v>
       </c>
       <c r="D21" s="23" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E21" s="24" t="s">
         <v>338</v>
@@ -15930,7 +15938,7 @@
         <v>375</v>
       </c>
       <c r="D23" s="23" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E23" s="24" t="s">
         <v>338</v>
@@ -16227,7 +16235,7 @@
         <v>183</v>
       </c>
       <c r="D36" s="23" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E36" s="24" t="s">
         <v>338</v>
@@ -16403,13 +16411,13 @@
         <v>45612.500390243054</v>
       </c>
       <c r="B44" s="23" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C44" s="23" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D44" s="23" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E44" s="24" t="s">
         <v>338</v>
@@ -16610,10 +16618,10 @@
         <v>45608.642259699074</v>
       </c>
       <c r="B53" s="23" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C53" s="23" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D53" s="23" t="s">
         <v>423</v>
@@ -16995,13 +17003,13 @@
         <v>45607.954778287036</v>
       </c>
       <c r="B70" s="23" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C70" s="23" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D70" s="23" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E70" s="24" t="s">
         <v>338</v>
@@ -17018,7 +17026,7 @@
         <v>45608.61292479167</v>
       </c>
       <c r="B71" s="23" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C71" s="23" t="s">
         <v>170</v>
@@ -17041,7 +17049,7 @@
         <v>45614.387590300925</v>
       </c>
       <c r="B72" s="23" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C72" s="23" t="s">
         <v>451</v>
@@ -17139,7 +17147,7 @@
         <v>458</v>
       </c>
       <c r="D76" s="23" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E76" s="24" t="s">
         <v>338</v>
@@ -17202,10 +17210,10 @@
         <v>45611.78726629629</v>
       </c>
       <c r="B79" s="23" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C79" s="23" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D79" s="23" t="s">
         <v>363</v>
@@ -17359,13 +17367,13 @@
         <v>45611.51554230324</v>
       </c>
       <c r="B86" s="23" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C86" s="23" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D86" s="23" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E86" s="24" t="s">
         <v>338</v>
@@ -17382,13 +17390,13 @@
         <v>45611.51554230324</v>
       </c>
       <c r="B87" s="23" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C87" s="23" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D87" s="23" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E87" s="24" t="s">
         <v>338</v>
@@ -17546,7 +17554,7 @@
         <v>482</v>
       </c>
       <c r="C94" s="23" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D94" s="23" t="s">
         <v>440</v>
@@ -17838,7 +17846,7 @@
         <v>45593.31507067129</v>
       </c>
       <c r="B107" s="23" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C107" s="23" t="s">
         <v>211</v>
@@ -18159,7 +18167,7 @@
         <v>305</v>
       </c>
       <c r="C121" s="23" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D121" s="23" t="s">
         <v>450</v>
@@ -18272,7 +18280,7 @@
         <v>167</v>
       </c>
       <c r="C126" s="23" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D126" s="23" t="s">
         <v>440</v>
@@ -18293,7 +18301,7 @@
         <v>519</v>
       </c>
       <c r="C127" s="23" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D127" s="23" t="s">
         <v>363</v>
@@ -18340,7 +18348,7 @@
         <v>367</v>
       </c>
       <c r="D129" s="23" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E129" s="24" t="s">
         <v>338</v>
@@ -18606,7 +18614,7 @@
         <v>45614.54105619213</v>
       </c>
       <c r="B141" s="23" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C141" s="23" t="s">
         <v>542</v>
@@ -18632,7 +18640,7 @@
         <v>352</v>
       </c>
       <c r="C142" s="23" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D142" s="23" t="s">
         <v>536</v>
@@ -18767,7 +18775,7 @@
         <v>372</v>
       </c>
       <c r="D148" s="23" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E148" s="24" t="s">
         <v>530</v>
@@ -18970,7 +18978,7 @@
         <v>183</v>
       </c>
       <c r="D157" s="23" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E157" s="24" t="s">
         <v>530</v>
@@ -19171,7 +19179,7 @@
         <v>45615.670564224536</v>
       </c>
       <c r="B166" s="23" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C166" s="23" t="s">
         <v>580</v>
@@ -19259,7 +19267,7 @@
         <v>45608.78817241898</v>
       </c>
       <c r="B170" s="23" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C170" s="23" t="s">
         <v>585</v>
@@ -19282,7 +19290,7 @@
         <v>45614.64683212963</v>
       </c>
       <c r="B171" s="23" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C171" s="23" t="s">
         <v>586</v>
@@ -19303,7 +19311,7 @@
         <v>45615.55931131945</v>
       </c>
       <c r="B172" s="23" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C172" s="23" t="s">
         <v>587</v>
@@ -19327,10 +19335,10 @@
         <v>589</v>
       </c>
       <c r="C173" s="23" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D173" s="23" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E173" s="24" t="s">
         <v>530</v>
@@ -19531,7 +19539,7 @@
         <v>599</v>
       </c>
       <c r="D182" s="23" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E182" s="24" t="s">
         <v>530</v>
@@ -19969,7 +19977,7 @@
         <v>45608.54732484954</v>
       </c>
       <c r="B202" s="23" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C202" s="23" t="s">
         <v>211</v>
@@ -20274,7 +20282,7 @@
         <v>367</v>
       </c>
       <c r="D215" s="23" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E215" s="24" t="s">
         <v>530</v>
@@ -20291,7 +20299,7 @@
         <v>45616.643043414355</v>
       </c>
       <c r="B216" s="23" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C216" s="23" t="s">
         <v>631</v>
@@ -20419,7 +20427,7 @@
         <v>45617.48618103009</v>
       </c>
       <c r="B222" s="23" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C222" s="23" t="s">
         <v>640</v>
@@ -20461,7 +20469,7 @@
         <v>45617.49734002315</v>
       </c>
       <c r="B224" s="23" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C224" s="23" t="s">
         <v>643</v>

--- a/P&C reports.xlsx
+++ b/P&C reports.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -817,12 +817,40 @@
           <t>Entrambe le serate</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>nero</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>wdamiata@gmail.com</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Entrambe le serate</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>1</t>
         </is>

--- a/P&C reports.xlsx
+++ b/P&C reports.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -845,14 +845,42 @@
           <t>Entrambe le serate</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>1</t>
+      <c r="E15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Martina </t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Canfarotta</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>c.martina.02@gmail.com</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Entrambe le serate</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 </t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 </t>
         </is>
       </c>
     </row>

--- a/P&C reports.xlsx
+++ b/P&C reports.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -873,14 +873,42 @@
           <t>Entrambe le serate</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 </t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2 </t>
+      <c r="E16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nicolò </t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Orefice</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>nikor2001@libero.it</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Prima serata - 10 Dicembre 2025</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>

--- a/P&C reports.xlsx
+++ b/P&C reports.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -901,12 +901,40 @@
           <t>Prima serata - 10 Dicembre 2025</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Giorgio</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Franco</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>fgiorgiomg@gmail.com</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Prima serata - 10 Dicembre 2025</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>0</t>
         </is>

--- a/P&C reports.xlsx
+++ b/P&C reports.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -929,12 +929,40 @@
           <t>Prima serata - 10 Dicembre 2025</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
+      <c r="E18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Monica </t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gelfo </t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>monica.gelfo75@gmail.com</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Prima serata - 10 Dicembre 2025</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 Monica Gelfo e Maria Giacalone </t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
         <is>
           <t>0</t>
         </is>

--- a/P&C reports.xlsx
+++ b/P&C reports.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -962,9 +962,39 @@
           <t xml:space="preserve">2 Monica Gelfo e Maria Giacalone </t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Loredana</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Chiarenza</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>lorychiarenza72@gmail.com</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Seconda serata - 11 Dicembre 2025</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
         <is>
           <t>0</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
     </row>

--- a/P&C reports.xlsx
+++ b/P&C reports.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -992,9 +992,39 @@
           <t>0</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>4</t>
+      <c r="F20" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gabriele </t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Girelli</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>girelligabriele5@gmail.com</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Seconda serata - 11 Dicembre 2025</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>9</t>
         </is>
       </c>
     </row>

--- a/P&C reports.xlsx
+++ b/P&C reports.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1022,9 +1022,39 @@
           <t>0</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>9</t>
+      <c r="F21" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Adele</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Vitello</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>adyvitello@gmail.com</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Prima serata - 10 Dicembre 2025</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>

--- a/P&C reports.xlsx
+++ b/P&C reports.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1052,7 +1052,37 @@
           <t>2</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Matilde</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Giangreco</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>matilde.giangreco204@gmail.com</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Prima serata - 10 Dicembre 2025</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
         <is>
           <t>0</t>
         </is>

--- a/P&C reports.xlsx
+++ b/P&C reports.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1082,9 +1082,39 @@
           <t>1</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Loredana </t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chiarenza </t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Marcoruta67@gmail.com</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Seconda serata - 11 Dicembre 2025</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
         <is>
           <t>0</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
     </row>

--- a/P&C reports.xlsx
+++ b/P&C reports.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1112,9 +1112,39 @@
           <t>0</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>4</t>
+      <c r="F24" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Settimo </t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Catanzaro</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>parisigiulia9@gmail.com</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Seconda serata - 11 Dicembre 2025</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
     </row>

--- a/P&C reports.xlsx
+++ b/P&C reports.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1142,7 +1142,37 @@
           <t>0</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F25" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Settimo </t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Catanzaro</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>parisigiulia9@gmail.com</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Seconda serata - 11 Dicembre 2025</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
         <is>
           <t>2</t>
         </is>

--- a/P&C reports.xlsx
+++ b/P&C reports.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1172,9 +1172,39 @@
           <t>0</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2</t>
+      <c r="F26" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Claudio </t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Gelfo</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>sabgelfo@gmail.com</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Prima serata - 10 Dicembre 2025</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>

--- a/P&C reports.xlsx
+++ b/P&C reports.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1202,7 +1202,37 @@
           <t>1</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Andrea</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Falanga</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>andri.falanga@gmail.com</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Prima serata - 10 Dicembre 2025</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
         <is>
           <t>0</t>
         </is>

--- a/P&C reports.xlsx
+++ b/P&C reports.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1232,7 +1232,37 @@
           <t>2</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Francesca</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Maggio</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>parisigiulia9@gmail.com</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Prima serata - 10 Dicembre 2025</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
         <is>
           <t>0</t>
         </is>

--- a/P&C reports.xlsx
+++ b/P&C reports.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1262,7 +1262,37 @@
           <t>1</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Matilde</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Di Girolamo</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>digirolamo.matilde9@gmail.com</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Prima serata - 10 Dicembre 2025</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
         <is>
           <t>0</t>
         </is>

--- a/P&C reports.xlsx
+++ b/P&C reports.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1292,7 +1292,37 @@
           <t>1</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Riccardo</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Zarzana</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>riccardinozarzana@gmail.com</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Prima serata - 10 Dicembre 2025</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
         <is>
           <t>0</t>
         </is>

--- a/P&C reports.xlsx
+++ b/P&C reports.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1322,7 +1322,37 @@
           <t>1</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Marco</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Di maio</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>dimaiomarco27@gmail.com</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Prima serata - 10 Dicembre 2025</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
         <is>
           <t>0</t>
         </is>

--- a/P&C reports.xlsx
+++ b/P&C reports.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1352,7 +1352,37 @@
           <t>1</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Lorenzo</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Viviano</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>lorenzov848@gmail.com</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Prima serata - 10 Dicembre 2025</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
         <is>
           <t>0</t>
         </is>

--- a/P&C reports.xlsx
+++ b/P&C reports.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1382,9 +1382,39 @@
           <t>1</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Salvatore </t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Miccich</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>parisigiulia9@gmail.com</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Seconda serata - 11 Dicembre 2025</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
         <is>
           <t>0</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>

--- a/P&C reports.xlsx
+++ b/P&C reports.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1412,9 +1412,39 @@
           <t>0</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F34" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Samuele</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Morvillo</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Samuelemorvillo@gmail.com</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Prima serata - 10 Dicembre 2025</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>

--- a/P&C reports.xlsx
+++ b/P&C reports.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1442,7 +1442,37 @@
           <t>1</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Giulio</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Accardo</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>giulio.accardo@community.unipa.it</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Prima serata - 10 Dicembre 2025</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
         <is>
           <t>0</t>
         </is>

--- a/P&C reports.xlsx
+++ b/P&C reports.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1472,7 +1472,37 @@
           <t>1</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Gaia</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Culotta</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Gaia.culotta@gmail.com</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Prima serata - 10 Dicembre 2025</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
         <is>
           <t>0</t>
         </is>

--- a/P&C reports.xlsx
+++ b/P&C reports.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1502,7 +1502,37 @@
           <t>1</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Chiara</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Lo Bello</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>chiaralobello89@gmail.com</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Prima serata - 10 Dicembre 2025</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
         <is>
           <t>0</t>
         </is>

--- a/P&C reports.xlsx
+++ b/P&C reports.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F38"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1532,7 +1532,37 @@
           <t>3</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Christian</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Barresi</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Trm.christian@gmail.com</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Prima serata - 10 Dicembre 2025</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
         <is>
           <t>0</t>
         </is>

--- a/P&C reports.xlsx
+++ b/P&C reports.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1562,7 +1562,37 @@
           <t>1</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Gaspare</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Catalano</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>gasparecatalano80@gmail.com</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Prima serata - 10 Dicembre 2025</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
         <is>
           <t>0</t>
         </is>

--- a/P&C reports.xlsx
+++ b/P&C reports.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1592,7 +1592,37 @@
           <t>1</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Giuseppe </t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Guerrera</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>parisigiulia9@gmail.com</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Prima serata - 10 Dicembre 2025</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
         <is>
           <t>0</t>
         </is>

--- a/P&C reports.xlsx
+++ b/P&C reports.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1622,9 +1622,39 @@
           <t>4</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="F41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Luisa</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Lombardo</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>lombardo.luisa01@gmail.com</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Seconda serata - 11 Dicembre 2025</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
         <is>
           <t>0</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
     </row>

--- a/P&C reports.xlsx
+++ b/P&C reports.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1652,9 +1652,39 @@
           <t>0</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="F42" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Rosalia</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Caminita </t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>parisigiulia9@gmail.com</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Prima serata - 10 Dicembre 2025</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
         <is>
           <t>3</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>

--- a/P&C reports.xlsx
+++ b/P&C reports.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1682,9 +1682,39 @@
           <t>3</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="F43" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Davide</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Diprima</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>davidediprima6@gmail.com</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Seconda serata - 11 Dicembre 2025</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
         <is>
           <t>0</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
     </row>

--- a/P&C reports.xlsx
+++ b/P&C reports.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:F45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1712,9 +1712,39 @@
           <t>0</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>2</t>
+      <c r="F44" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Marianna</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Ferraroni</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>mariannaferraroni@libero.it</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Prima serata - 10 Dicembre 2025</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>

--- a/P&C reports.xlsx
+++ b/P&C reports.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F45"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1742,7 +1742,37 @@
           <t>1</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="F45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Giovanna</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Caminita</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>parisigiulia9@gmail.com</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Prima serata - 10 Dicembre 2025</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
         <is>
           <t>0</t>
         </is>

--- a/P&C reports.xlsx
+++ b/P&C reports.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:F47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1772,7 +1772,37 @@
           <t>3</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Silvana </t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Anania</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Marcoruta67@gmail.com</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Prima serata - 10 Dicembre 2025</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
         <is>
           <t>0</t>
         </is>

--- a/P&C reports.xlsx
+++ b/P&C reports.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F47"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1802,9 +1802,39 @@
           <t>4</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="F47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MariaValeria </t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pomello </t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Marcoruta67@gmail.com</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Seconda serata - 11 Dicembre 2025</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
         <is>
           <t>0</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
     </row>

--- a/P&C reports.xlsx
+++ b/P&C reports.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F48"/>
+  <dimension ref="A1:F49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1832,9 +1832,39 @@
           <t>0</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>3</t>
+      <c r="F48" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Maria Chiara</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Messina </t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>messinamariachiara37@gmail.com</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Prima serata - 10 Dicembre 2025</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>

--- a/P&C reports.xlsx
+++ b/P&C reports.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F49"/>
+  <dimension ref="A1:F50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1862,9 +1862,39 @@
           <t>1</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="F49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rosy </t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>La Malfa</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>parisigiulia9@gmail.com</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Seconda serata - 11 Dicembre 2025</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
         <is>
           <t>0</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
     </row>

--- a/P&C reports.xlsx
+++ b/P&C reports.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F50"/>
+  <dimension ref="A1:F51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1892,9 +1892,39 @@
           <t>0</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>3</t>
+      <c r="F50" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Noemi</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Schiavo</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>noemischiavo27@gmail.com</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Prima serata - 10 Dicembre 2025</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>

--- a/P&C reports.xlsx
+++ b/P&C reports.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F51"/>
+  <dimension ref="A1:F52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1922,7 +1922,37 @@
           <t>1</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="F51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Francesco</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Palazzo</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>parisigiulia9@gmail.com</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Prima serata - 10 Dicembre 2025</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
         <is>
           <t>0</t>
         </is>

--- a/P&C reports.xlsx
+++ b/P&C reports.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F52"/>
+  <dimension ref="A1:F53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1952,7 +1952,37 @@
           <t>3</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="F52" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Chiara</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lipari </t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chiara03.lipari@gmail.com </t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Prima serata - 10 Dicembre 2025</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
         <is>
           <t>0</t>
         </is>

--- a/P&C reports.xlsx
+++ b/P&C reports.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F53"/>
+  <dimension ref="A1:F54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1982,7 +1982,37 @@
           <t>1</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="F53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Federico </t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sperandeo </t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>fedesperax@gmail.com</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Prima serata - 10 Dicembre 2025</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
         <is>
           <t>0</t>
         </is>

--- a/P&C reports.xlsx
+++ b/P&C reports.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F54"/>
+  <dimension ref="A1:F55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2012,7 +2012,37 @@
           <t>1</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="F54" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Ludovica</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Bentivegna</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>ludovicabenti.04@gmail.com</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Prima serata - 10 Dicembre 2025</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
         <is>
           <t>0</t>
         </is>

--- a/P&C reports.xlsx
+++ b/P&C reports.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F55"/>
+  <dimension ref="A1:F56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2042,9 +2042,39 @@
           <t>1</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="F55" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Giovanni</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Azzara</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>azzaragiovanni91@gmail.com</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Seconda serata - 11 Dicembre 2025</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
         <is>
           <t>0</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
     </row>

--- a/P&C reports.xlsx
+++ b/P&C reports.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F56"/>
+  <dimension ref="A1:F57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2072,9 +2072,39 @@
           <t>0</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="F56" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Alessia</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Arnone</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>alearnone26@gmail.com</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Prima serata - 10 Dicembre 2025</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
         <is>
           <t>3</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>

--- a/P&C reports.xlsx
+++ b/P&C reports.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F57"/>
+  <dimension ref="A1:F58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2102,7 +2102,37 @@
           <t>3</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="F57" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Cristina</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Amato</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>cristina.amato97@gmail.com</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Prima serata - 10 Dicembre 2025</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
         <is>
           <t>0</t>
         </is>

--- a/P&C reports.xlsx
+++ b/P&C reports.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F58"/>
+  <dimension ref="A1:F59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2132,7 +2132,37 @@
           <t>2</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="F58" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Iolanda</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Agnese</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Iolanda.agnese@libero.it</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Prima serata - 10 Dicembre 2025</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 </t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
         <is>
           <t>0</t>
         </is>

--- a/P&C reports.xlsx
+++ b/P&C reports.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F59"/>
+  <dimension ref="A1:F60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2162,9 +2162,39 @@
           <t xml:space="preserve">1 </t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="F59" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Loredana</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Carta</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>sabgelfo@gmail.com</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Seconda serata - 11 Dicembre 2025</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
         <is>
           <t>0</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
     </row>

--- a/P&C reports.xlsx
+++ b/P&C reports.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F60"/>
+  <dimension ref="A1:F61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2192,9 +2192,39 @@
           <t>0</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>2</t>
+      <c r="F60" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Roberta</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Acquisto</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>roberta.acquisto00@gmail.com</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Prima serata - 10 Dicembre 2025</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>

--- a/P&C reports.xlsx
+++ b/P&C reports.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F61"/>
+  <dimension ref="A1:F62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2222,9 +2222,39 @@
           <t>1</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="F61" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Antonino </t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Santino</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>antonino.santino@libero.it</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Seconda serata - 11 Dicembre 2025</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
         <is>
           <t>0</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
     </row>

--- a/P&C reports.xlsx
+++ b/P&C reports.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F62"/>
+  <dimension ref="A1:F63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2252,9 +2252,39 @@
           <t>0</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>3</t>
+      <c r="F62" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Elena </t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Belvedere </t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>parisigiulia9@gmail.com</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Prima serata - 10 Dicembre 2025</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>

--- a/P&C reports.xlsx
+++ b/P&C reports.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F63"/>
+  <dimension ref="A1:F64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2282,9 +2282,39 @@
           <t>1</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
+      <c r="F63" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Barbara</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Cassara</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Barbaracassara80@gmail.com</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Seconda serata - 11 Dicembre 2025</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
         <is>
           <t>0</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
     </row>

--- a/P&C reports.xlsx
+++ b/P&C reports.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F64"/>
+  <dimension ref="A1:F65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2312,9 +2312,39 @@
           <t>0</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>3</t>
+      <c r="F64" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Andrea</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Filloramo </t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>roandri2013@gmail.com</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Seconda serata - 11 Dicembre 2025</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>

--- a/P&C reports.xlsx
+++ b/P&C reports.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F65"/>
+  <dimension ref="A1:F66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2342,9 +2342,39 @@
           <t>0</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>1</t>
+      <c r="F65" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Emanuela </t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ventimiglia </t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>parisigiulia9@gmail.com</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Seconda serata - 11 Dicembre 2025</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
     </row>

--- a/P&C reports.xlsx
+++ b/P&C reports.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F66"/>
+  <dimension ref="A1:F67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2372,7 +2372,37 @@
           <t>0</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
+      <c r="F66" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Chiara</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Guglia</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>parisigiulia9@gmail.com</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Seconda serata - 11 Dicembre 2025</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
         <is>
           <t>2</t>
         </is>

--- a/P&C reports.xlsx
+++ b/P&C reports.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F67"/>
+  <dimension ref="A1:F68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2402,7 +2402,37 @@
           <t>0</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="F67" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Mariachiara</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Chiarella</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>parisigiulia9@gmail.com</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Seconda serata - 11 Dicembre 2025</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
         <is>
           <t>2</t>
         </is>

--- a/P&C reports.xlsx
+++ b/P&C reports.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F68"/>
+  <dimension ref="A1:F69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2432,9 +2432,39 @@
           <t>0</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>2</t>
+      <c r="F68" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Vittoria</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Cappello</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>cappellovittoria13@gmail.com</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Seconda serata - 11 Dicembre 2025</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>

--- a/P&C reports.xlsx
+++ b/P&C reports.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F69"/>
+  <dimension ref="A1:F70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2462,7 +2462,37 @@
           <t>0</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
+      <c r="F69" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Federico </t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Damiata</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>damiatafederico@gmail.com</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Seconda serata - 11 Dicembre 2025</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
         <is>
           <t>1</t>
         </is>

--- a/P&C reports.xlsx
+++ b/P&C reports.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F70"/>
+  <dimension ref="A1:F71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2492,9 +2492,39 @@
           <t>0</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>1</t>
+      <c r="F70" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>roberto</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ingargiola </t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>ingargeom99@gmail.com</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Seconda serata - 11 Dicembre 2025</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
     </row>
